--- a/data/resumes/parsed.xlsx
+++ b/data/resumes/parsed.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -486,9 +486,82 @@
         <v>2026-03-07T21:05:49.209Z</v>
       </c>
     </row>
+    <row r="3" xml:space="preserve">
+      <c r="A3" t="str">
+        <v>majipanthadip@gmail.com</v>
+      </c>
+      <c r="B3" t="str" xml:space="preserve">
+        <v xml:space="preserve">
+PANTHADIP MAJI  |  20EE37001
+ELECT.ENGG. INSTRUMENTATION AND INTEGRATED ELECTRONICS(M.Tech Dual 5Y)
+EDUCATION
+YearDegree/ExamInstituteCGPA/Marks
+2025M.TECH Dual Degree 5YIIT Kharagpur7.86 / 10
+2020XII: WBCHSEBankura Banga Vidyalaya97%
+2018X: WBBSEGarh Raipur High School (H.S)94.57%
+INTERNSHIPS
+Analog Signal Processing for Seismic Application | Prof. Debashis Mandal | IIT KGP                                    May'24 - Jul'24
+• Learned concept of Geophone,capacitive MEMS Accelerometer,Nature of Seismic Signals &amp; Existing methods of sensing Seismic signals.
+• Designed ASP circuit having OTA with o/p CM Feedback. DM &amp; CM Loop Gain, PM, UGB 65dB, 68deg, 3.5MHz &amp; 58dB, 60deg, 1.7MHz. 
+• Applied Chop-Dechop to reduce the noise, 2nd Integrator to extract acceleration to velocity information so that geophone is not needed.
+In-Memory Computing Techniques(IMC) | Prof. Kaushik Roy | Purdue University                                           May'23 - Jul'23
+• Analysed different types of Single Slope ADCs &amp; Designed variations of the Current Comparator Based SSADCs, tsmc65nm technology.
+• Designed Auto-Calibration Scheme(Counters, PIPO Register, Current Ramp Generator) for Monte Carlo Variations converge to ideal one.
+• Designed a scheme of Voltage Mode SSADC, i.e., Integrator Opamp(as TIA) + Voltage Mode Comparator based (Current Mode Crossbar).
+High-Speed SERDES Design | Prof. Mrigank Sharad | IIT KGP &amp; ISRO Collab                                                Aug’22 - Dec’22
+• The Project involves the design of a High-Speed (2GPS) Radiation Hardened Serialiser-Deserialiser design in 180nm SCL Technology.
+• Completed the custom layout &amp;  post-layout verification containing RX, CDR, SIPO register, Comma detection ckt &amp; Word alignment ckt.
+• Done layout integration of whole receiver side(Includes RX, CDR, Comma-Detector, De-serializer &amp; Decoder) with post-layout verification.
+PROJECTS
+Programmable fractional-N frequency divider | MSCSoc Lab Project                                                               Jan’24 - Apr’24
+• The project involves a programmable fractional-N frequency divider where fin = 2.2 to 2.6GHz, fout = 100MHz, power consumption 5mW.
+• Designed existing Multi-modulus frequency divider based topology (2/3 Prescalar Module, Programmable Divider, DSDM) in 180nm SCL.
+• Main contribution to power loss was from multiple 2/3 prescaler cells present in multi-modulus to mitigate implemented fast CML logic.
+Signal acquisition front end using VCO based 1-1 MASH SDM | Bachelor’s Thesis Project                          Jan’24 - Apr’24
+• I have thoroughly learned the concept of Sigma-Delta Modulator (SDM), Noise Shaping &amp; Multi-Stage Noise Shaping (MASH) architecture.
+• Designed existing VCO-based topology(Gm stage,Differential CCO,Level enhancer,Counters &amp; Differentiator, Delay Element, Subtractor).
+• Verified 1st order &amp;2nd order noise shaping coming from two consecutive stages of VCO based 1-1 MASH SDM Architecture, tsmc65nm.
+Seizure Onset Detection | Summer VLSI Course Project                                                                                   Apr’22 - May’22
+•  Designed Seizure Onset Detection circuit that can correctly measure greater than 200Hz &amp;  maximum duration of 3.35 sec onset signal.
+•  Designed &amp; simulated Differential Amplifier(Open Loop Gain 60.8dB, 142KHz BW, 40deg PM), Envelope Detector,Comparator in LT Spice.
+TRAINING
+Gaussmeter Using Hall Sensor &amp; ESP32 Microcontroller | INS Design Lab                                                     Jan’24 - Apr’24
+• Made Gaussmeter (i/p: -1000 to +1000Gauss) using Honeywell SS49E Hall sensor, INA to eliminate noise, 16bit ADC. ESP32 &amp; LCD Display.
+• Used 12V Lipo battery with a buck converter generating a 5V supply and a boost converter providing +12V and -12V supplies for the INA.
+• Completed Breadboard verification, veroboard verification, designed &amp; fabricated PCB using Kicad, completed the casing using Autocad.
+Summer VLSI Course                                                                                                                                             Apr’22 - May’22
+• Specialized in mixed signal circuit elements like multi-stage Op-Amps, OTAs, TIA, Sensor Interface, and LDOs (Low Dropout Regulators).
+• Performed transistor-level simulations on each circuit element to address practical problems and optimized for sizing, stability, power, etc.
+PUBLICATIONS
+Submitted a paper named "Approximate ADCs for In-Memory Computing" to IEEE Transactions on Neural Networks and Learning Systems.
+SKILLS AND EXPERTISE
+Programming Languages:   MATLAB | C |  C++ |  Verilog | VerilogA |  AVR ATMEGA32 Language   |  Python |  HTML  |  CSS | JavaScript
+Softwares: Cadence Virtuoso | MATLAB | LT Spice | Easy EDA | Microchip Studio | Circuit maker | Tina Ti | VS Code | Proteus | Autocad 
+COURSEWORK INFORMATION
+Analog &amp; Digital Courses:  Analog Electronic Circuits*   |  Digital Electronic Circuits*  |   Analog Signal Processing  |  Digital Signal
+Processing* | Digital VLSI Circuits | Mixed Signal Circuits &amp; System On Chip* | Radio Frequency Integrated Circuits | Power Management IC
+Electrical Core Courses:  Control System*  |  Power Systems*  |  Embedded Systems* |  Power Electronics*  |  Electrical Machines*
+Computer Science Courses:  Programming and Data Structures in C*   |   Computer Architecture &amp;  Operating System  (*indicates lab)
+Other Courses:  Probability &amp; Statistics | Linear Algebra, Numerical &amp; Complex Analysis | Advance Calculus | Introduction to Reliability
+| Advance Sensing Techniques* | Signals and Systems* | Modelling &amp; Identification | Data Communication | Sensors &amp;Measurement Tech
+POSITIONS OF RESPONSIBILITY
+•  Performed the role of Vice Captain in the "Eastern Instrumentals" group at Azad Hall of Residence.                                   Aug’23 - Dec’23
+•  Performed role as TA for NPTEL Online Certification Course, ”Analog Circuits and Systems through SPICE Simulation”.    Jan’23 - Apr’23
+EXTRA CURRICULAR ACTIVITIES
+Tabla Player, Inter Hall Championship Groups, Azad Hall of Residence | Leader of the NSS Swachh Bharat Abhiyan Rally | As a co-guide
+of Vocals and Instrumentals, serving as Tabla Player | Part of Open IIT Product Design competition with Efficient Cart Modelling
+!Self declared by the student, CDC could not verify the relevant documents</v>
+      </c>
+      <c r="C3" t="str">
+        <v>1772926457704-754730388.pdf</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-03-07T23:34:18.704Z</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/resumes/parsed.xlsx
+++ b/data/resumes/parsed.xlsx
@@ -1,41 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PANTHADIP MAJI\Downloads\quantedge-portal\data\resumes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688E3239-7439-4852-A204-B0FAE9ADF62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>ResumeText</t>
+  </si>
+  <si>
+    <t>FileName</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -65,13 +68,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,172 +407,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Email</v>
+    <row r="1" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
       </c>
-      <c r="B1" t="str">
-        <v>ResumeText</v>
+      <c r="B1" t="s">
+        <v>1</v>
       </c>
-      <c r="C1" t="str">
-        <v>FileName</v>
+      <c r="C1" t="s">
+        <v>2</v>
       </c>
-      <c r="D1" t="str">
-        <v>Timestamp</v>
+      <c r="D1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2" xml:space="preserve">
-      <c r="A2" t="str">
-        <v>majipanthadip@gmail.com</v>
-      </c>
-      <c r="B2" t="str" xml:space="preserve">
-        <v xml:space="preserve">
-PANTHADIP MAJI  |  20EE37001
-ELECT.ENGG. INSTRUMENTATION AND INTEGRATED ELECTRONICS(M.Tech Dual 5Y)
-EDUCATION
-YearDegree/ExamInstituteCGPA/Marks
-2025M.TECH Dual Degree 5YIIT Kharagpur7.86 / 10
-2020XII: WBCHSEBankura Banga Vidyalaya97%
-2018X: WBBSEGarh Raipur High School (H.S)94.57%
-INTERNSHIPS
-Analog Signal Processing for Seismic Application | Prof. Debashis Mandal | IIT KGP                                    May'24 - Jul'24
-• Learned concept of Geophone,capacitive MEMS Accelerometer,Nature of Seismic Signals &amp; Existing methods of sensing Seismic signals.
-• Designed ASP circuit having OTA with o/p CM Feedback. DM &amp; CM Loop Gain, PM, UGB 65dB, 68deg, 3.5MHz &amp; 58dB, 60deg, 1.7MHz. 
-• Applied Chop-Dechop to reduce the noise, 2nd Integrator to extract acceleration to velocity information so that geophone is not needed.
-In-Memory Computing Techniques(IMC) | Prof. Kaushik Roy | Purdue University                                           May'23 - Jul'23
-• Analysed different types of Single Slope ADCs &amp; Designed variations of the Current Comparator Based SSADCs, tsmc65nm technology.
-• Designed Auto-Calibration Scheme(Counters, PIPO Register, Current Ramp Generator) for Monte Carlo Variations converge to ideal one.
-• Designed a scheme of Voltage Mode SSADC, i.e., Integrator Opamp(as TIA) + Voltage Mode Comparator based (Current Mode Crossbar).
-High-Speed SERDES Design | Prof. Mrigank Sharad | IIT KGP &amp; ISRO Collab                                                Aug’22 - Dec’22
-• The Project involves the design of a High-Speed (2GPS) Radiation Hardened Serialiser-Deserialiser design in 180nm SCL Technology.
-• Completed the custom layout &amp;  post-layout verification containing RX, CDR, SIPO register, Comma detection ckt &amp; Word alignment ckt.
-• Done layout integration of whole receiver side(Includes RX, CDR, Comma-Detector, De-serializer &amp; Decoder) with post-layout verification.
-PROJECTS
-Programmable fractional-N frequency divider | MSCSoc Lab Project                                                               Jan’24 - Apr’24
-• The project involves a programmable fractional-N frequency divider where fin = 2.2 to 2.6GHz, fout = 100MHz, power consumption 5mW.
-• Designed existing Multi-modulus frequency divider based topology (2/3 Prescalar Module, Programmable Divider, DSDM) in 180nm SCL.
-• Main contribution to power loss was from multiple 2/3 prescaler cells present in multi-modulus to mitigate implemented fast CML logic.
-Signal acquisition front end using VCO based 1-1 MASH SDM | Bachelor’s Thesis Project                          Jan’24 - Apr’24
-• I have thoroughly learned the concept of Sigma-Delta Modulator (SDM), Noise Shaping &amp; Multi-Stage Noise Shaping (MASH) architecture.
-• Designed existing VCO-based topology(Gm stage,Differential CCO,Level enhancer,Counters &amp; Differentiator, Delay Element, Subtractor).
-• Verified 1st order &amp;2nd order noise shaping coming from two consecutive stages of VCO based 1-1 MASH SDM Architecture, tsmc65nm.
-Seizure Onset Detection | Summer VLSI Course Project                                                                                   Apr’22 - May’22
-•  Designed Seizure Onset Detection circuit that can correctly measure greater than 200Hz &amp;  maximum duration of 3.35 sec onset signal.
-•  Designed &amp; simulated Differential Amplifier(Open Loop Gain 60.8dB, 142KHz BW, 40deg PM), Envelope Detector,Comparator in LT Spice.
-TRAINING
-Gaussmeter Using Hall Sensor &amp; ESP32 Microcontroller | INS Design Lab                                                     Jan’24 - Apr’24
-• Made Gaussmeter (i/p: -1000 to +1000Gauss) using Honeywell SS49E Hall sensor, INA to eliminate noise, 16bit ADC. ESP32 &amp; LCD Display.
-• Used 12V Lipo battery with a buck converter generating a 5V supply and a boost converter providing +12V and -12V supplies for the INA.
-• Completed Breadboard verification, veroboard verification, designed &amp; fabricated PCB using Kicad, completed the casing using Autocad.
-Summer VLSI Course                                                                                                                                             Apr’22 - May’22
-• Specialized in mixed signal circuit elements like multi-stage Op-Amps, OTAs, TIA, Sensor Interface, and LDOs (Low Dropout Regulators).
-• Performed transistor-level simulations on each circuit element to address practical problems and optimized for sizing, stability, power, etc.
-PUBLICATIONS
-Submitted a paper named "Approximate ADCs for In-Memory Computing" to IEEE Transactions on Neural Networks and Learning Systems.
-SKILLS AND EXPERTISE
-Programming Languages:   MATLAB | C |  C++ |  Verilog | VerilogA |  AVR ATMEGA32 Language   |  Python |  HTML  |  CSS | JavaScript
-Softwares: Cadence Virtuoso | MATLAB | LT Spice | Easy EDA | Microchip Studio | Circuit maker | Tina Ti | VS Code | Proteus | Autocad 
-COURSEWORK INFORMATION
-Analog &amp; Digital Courses:  Analog Electronic Circuits*   |  Digital Electronic Circuits*  |   Analog Signal Processing  |  Digital Signal
-Processing* | Digital VLSI Circuits | Mixed Signal Circuits &amp; System On Chip* | Radio Frequency Integrated Circuits | Power Management IC
-Electrical Core Courses:  Control System*  |  Power Systems*  |  Embedded Systems* |  Power Electronics*  |  Electrical Machines*
-Computer Science Courses:  Programming and Data Structures in C*   |   Computer Architecture &amp;  Operating System  (*indicates lab)
-Other Courses:  Probability &amp; Statistics | Linear Algebra, Numerical &amp; Complex Analysis | Advance Calculus | Introduction to Reliability
-| Advance Sensing Techniques* | Signals and Systems* | Modelling &amp; Identification | Data Communication | Sensors &amp;Measurement Tech
-POSITIONS OF RESPONSIBILITY
-•  Performed the role of Vice Captain in the "Eastern Instrumentals" group at Azad Hall of Residence.                                   Aug’23 - Dec’23
-•  Performed role as TA for NPTEL Online Certification Course, ”Analog Circuits and Systems through SPICE Simulation”.    Jan’23 - Apr’23
-EXTRA CURRICULAR ACTIVITIES
-Tabla Player, Inter Hall Championship Groups, Azad Hall of Residence | Leader of the NSS Swachh Bharat Abhiyan Rally | As a co-guide
-of Vocals and Instrumentals, serving as Tabla Player | Part of Open IIT Product Design competition with Efficient Cart Modelling
-!Self declared by the student, CDC could not verify the relevant documents</v>
-      </c>
-      <c r="C2" t="str">
-        <v>1772917548754-251139681.pdf</v>
-      </c>
-      <c r="D2" t="str">
-        <v>2026-03-07T21:05:49.209Z</v>
-      </c>
-    </row>
-    <row r="3" xml:space="preserve">
-      <c r="A3" t="str">
-        <v>majipanthadip@gmail.com</v>
-      </c>
-      <c r="B3" t="str" xml:space="preserve">
-        <v xml:space="preserve">
-PANTHADIP MAJI  |  20EE37001
-ELECT.ENGG. INSTRUMENTATION AND INTEGRATED ELECTRONICS(M.Tech Dual 5Y)
-EDUCATION
-YearDegree/ExamInstituteCGPA/Marks
-2025M.TECH Dual Degree 5YIIT Kharagpur7.86 / 10
-2020XII: WBCHSEBankura Banga Vidyalaya97%
-2018X: WBBSEGarh Raipur High School (H.S)94.57%
-INTERNSHIPS
-Analog Signal Processing for Seismic Application | Prof. Debashis Mandal | IIT KGP                                    May'24 - Jul'24
-• Learned concept of Geophone,capacitive MEMS Accelerometer,Nature of Seismic Signals &amp; Existing methods of sensing Seismic signals.
-• Designed ASP circuit having OTA with o/p CM Feedback. DM &amp; CM Loop Gain, PM, UGB 65dB, 68deg, 3.5MHz &amp; 58dB, 60deg, 1.7MHz. 
-• Applied Chop-Dechop to reduce the noise, 2nd Integrator to extract acceleration to velocity information so that geophone is not needed.
-In-Memory Computing Techniques(IMC) | Prof. Kaushik Roy | Purdue University                                           May'23 - Jul'23
-• Analysed different types of Single Slope ADCs &amp; Designed variations of the Current Comparator Based SSADCs, tsmc65nm technology.
-• Designed Auto-Calibration Scheme(Counters, PIPO Register, Current Ramp Generator) for Monte Carlo Variations converge to ideal one.
-• Designed a scheme of Voltage Mode SSADC, i.e., Integrator Opamp(as TIA) + Voltage Mode Comparator based (Current Mode Crossbar).
-High-Speed SERDES Design | Prof. Mrigank Sharad | IIT KGP &amp; ISRO Collab                                                Aug’22 - Dec’22
-• The Project involves the design of a High-Speed (2GPS) Radiation Hardened Serialiser-Deserialiser design in 180nm SCL Technology.
-• Completed the custom layout &amp;  post-layout verification containing RX, CDR, SIPO register, Comma detection ckt &amp; Word alignment ckt.
-• Done layout integration of whole receiver side(Includes RX, CDR, Comma-Detector, De-serializer &amp; Decoder) with post-layout verification.
-PROJECTS
-Programmable fractional-N frequency divider | MSCSoc Lab Project                                                               Jan’24 - Apr’24
-• The project involves a programmable fractional-N frequency divider where fin = 2.2 to 2.6GHz, fout = 100MHz, power consumption 5mW.
-• Designed existing Multi-modulus frequency divider based topology (2/3 Prescalar Module, Programmable Divider, DSDM) in 180nm SCL.
-• Main contribution to power loss was from multiple 2/3 prescaler cells present in multi-modulus to mitigate implemented fast CML logic.
-Signal acquisition front end using VCO based 1-1 MASH SDM | Bachelor’s Thesis Project                          Jan’24 - Apr’24
-• I have thoroughly learned the concept of Sigma-Delta Modulator (SDM), Noise Shaping &amp; Multi-Stage Noise Shaping (MASH) architecture.
-• Designed existing VCO-based topology(Gm stage,Differential CCO,Level enhancer,Counters &amp; Differentiator, Delay Element, Subtractor).
-• Verified 1st order &amp;2nd order noise shaping coming from two consecutive stages of VCO based 1-1 MASH SDM Architecture, tsmc65nm.
-Seizure Onset Detection | Summer VLSI Course Project                                                                                   Apr’22 - May’22
-•  Designed Seizure Onset Detection circuit that can correctly measure greater than 200Hz &amp;  maximum duration of 3.35 sec onset signal.
-•  Designed &amp; simulated Differential Amplifier(Open Loop Gain 60.8dB, 142KHz BW, 40deg PM), Envelope Detector,Comparator in LT Spice.
-TRAINING
-Gaussmeter Using Hall Sensor &amp; ESP32 Microcontroller | INS Design Lab                                                     Jan’24 - Apr’24
-• Made Gaussmeter (i/p: -1000 to +1000Gauss) using Honeywell SS49E Hall sensor, INA to eliminate noise, 16bit ADC. ESP32 &amp; LCD Display.
-• Used 12V Lipo battery with a buck converter generating a 5V supply and a boost converter providing +12V and -12V supplies for the INA.
-• Completed Breadboard verification, veroboard verification, designed &amp; fabricated PCB using Kicad, completed the casing using Autocad.
-Summer VLSI Course                                                                                                                                             Apr’22 - May’22
-• Specialized in mixed signal circuit elements like multi-stage Op-Amps, OTAs, TIA, Sensor Interface, and LDOs (Low Dropout Regulators).
-• Performed transistor-level simulations on each circuit element to address practical problems and optimized for sizing, stability, power, etc.
-PUBLICATIONS
-Submitted a paper named "Approximate ADCs for In-Memory Computing" to IEEE Transactions on Neural Networks and Learning Systems.
-SKILLS AND EXPERTISE
-Programming Languages:   MATLAB | C |  C++ |  Verilog | VerilogA |  AVR ATMEGA32 Language   |  Python |  HTML  |  CSS | JavaScript
-Softwares: Cadence Virtuoso | MATLAB | LT Spice | Easy EDA | Microchip Studio | Circuit maker | Tina Ti | VS Code | Proteus | Autocad 
-COURSEWORK INFORMATION
-Analog &amp; Digital Courses:  Analog Electronic Circuits*   |  Digital Electronic Circuits*  |   Analog Signal Processing  |  Digital Signal
-Processing* | Digital VLSI Circuits | Mixed Signal Circuits &amp; System On Chip* | Radio Frequency Integrated Circuits | Power Management IC
-Electrical Core Courses:  Control System*  |  Power Systems*  |  Embedded Systems* |  Power Electronics*  |  Electrical Machines*
-Computer Science Courses:  Programming and Data Structures in C*   |   Computer Architecture &amp;  Operating System  (*indicates lab)
-Other Courses:  Probability &amp; Statistics | Linear Algebra, Numerical &amp; Complex Analysis | Advance Calculus | Introduction to Reliability
-| Advance Sensing Techniques* | Signals and Systems* | Modelling &amp; Identification | Data Communication | Sensors &amp;Measurement Tech
-POSITIONS OF RESPONSIBILITY
-•  Performed the role of Vice Captain in the "Eastern Instrumentals" group at Azad Hall of Residence.                                   Aug’23 - Dec’23
-•  Performed role as TA for NPTEL Online Certification Course, ”Analog Circuits and Systems through SPICE Simulation”.    Jan’23 - Apr’23
-EXTRA CURRICULAR ACTIVITIES
-Tabla Player, Inter Hall Championship Groups, Azad Hall of Residence | Leader of the NSS Swachh Bharat Abhiyan Rally | As a co-guide
-of Vocals and Instrumentals, serving as Tabla Player | Part of Open IIT Product Design competition with Efficient Cart Modelling
-!Self declared by the student, CDC could not verify the relevant documents</v>
-      </c>
-      <c r="C3" t="str">
-        <v>1772926457704-754730388.pdf</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-03-07T23:34:18.704Z</v>
-      </c>
-    </row>
+    <row r="2" spans="1:4" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="1:4" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D3"/>
+    <ignoredError sqref="A1:D1" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>